--- a/outputs/ZR751/parameters/MK-8669_parameters.xlsx
+++ b/outputs/ZR751/parameters/MK-8669_parameters.xlsx
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3383030175864389</v>
+        <v>0.3383023761020508</v>
       </c>
     </row>
     <row r="3">
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9206164450672484</v>
+        <v>0.9206165632146274</v>
       </c>
     </row>
     <row r="4">
@@ -448,7 +448,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001332272499388504</v>
+        <v>0.001332275803319502</v>
       </c>
     </row>
     <row r="5">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9683543620937756</v>
+        <v>0.9683520044005451</v>
       </c>
     </row>
   </sheetData>
